--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/12_Anlage_1_Auszahlungsvoraussetzungen.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/12_Anlage_1_Auszahlungsvoraussetzungen.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tranche_1" sheetId="1" r:id="Rcf31b4066bfb4b3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tranche_2" sheetId="2" r:id="Rb76ba0a7adc34f85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigabeprotokoll" sheetId="3" r:id="R9f4709e1a7aa46cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tranche_1" sheetId="1" r:id="R8eb2108d99794e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tranche_2" sheetId="2" r:id="R9b1d42c2b9b74176"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigabeprotokoll" sheetId="3" r:id="Rbf70cc5d75d34a17"/>
   </x:sheets>
 </x:workbook>
 </file>
